--- a/HumanBartender/outputs/20260915-content-editing/HumanBartender_Game_Settings.xlsx
+++ b/HumanBartender/outputs/20260915-content-editing/HumanBartender_Game_Settings.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R3aaccd5be5424327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="R6a12b67cae9c4dc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Days" sheetId="3" r:id="Ra24697d640c54314"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConfig" sheetId="4" r:id="Rd476b7cdc31340be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="5" r:id="R3e1e83b2bfd24aa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SettlementRules" sheetId="6" r:id="Rf5d66574d3404c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScoreBands" sheetId="7" r:id="R5e9e53fcab86462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AffinityMatrix" sheetId="8" r:id="R4802d4b6fd7c4332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocktails" sheetId="9" r:id="R71cf1a55c9124815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipes" sheetId="10" r:id="R174227f19f9c48cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CocktailTags" sheetId="11" r:id="R1f3ba9839c744f0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShelfItems" sheetId="12" r:id="R7444cea098cb4677"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tastes" sheetId="13" r:id="Rc33df9ba07a3450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWaves" sheetId="14" r:id="Rceaf79ff279b410a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegularSlots" sheetId="15" r:id="Rb000ed706f124179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personalities" sheetId="16" r:id="R7867c7fe70e3459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barks" sheetId="17" r:id="R69cb004e2775435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarkSituations" sheetId="18" r:id="R9cabc80bc53746fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestSettings" sheetId="19" r:id="R993396f83b814233"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestParts" sheetId="20" r:id="R92d6818a39364607"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestPersonalities" sheetId="21" r:id="R5c67b58703654e1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestExclusions" sheetId="22" r:id="R2a19626d0bb84bfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrderRules" sheetId="23" r:id="R7f00c81014a546b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="24" r:id="R1b74dc1a1269499c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transitions" sheetId="25" r:id="R3101a141e58f4430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIStrings" sheetId="26" r:id="Rcafa82887fdc4748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="27" r:id="Rfc1d502b6b0a4782"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="28" r:id="Rf4b4bfc5d8e54a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" r:id="R2b4603a6b4af4806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceInventory" sheetId="2" r:id="Rd17623bf6a7d464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Days" sheetId="3" r:id="R40fbf3fbcbcf46f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConfig" sheetId="4" r:id="R46966d41fe5e4c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="5" r:id="R10bd6b73f77c48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SettlementRules" sheetId="6" r:id="R24779ab630854301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScoreBands" sheetId="7" r:id="R57537846a3f544fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AffinityMatrix" sheetId="8" r:id="Rf1df453f82db46ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocktails" sheetId="9" r:id="Rd0cdbca849c64db1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipes" sheetId="10" r:id="Rb70222425597463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CocktailTags" sheetId="11" r:id="Rb2b9698a1ccd429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShelfItems" sheetId="12" r:id="R00d9657699674f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tastes" sheetId="13" r:id="Re041e84778d24088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWaves" sheetId="14" r:id="Red9601cc203c4405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegularSlots" sheetId="15" r:id="R46bf39607c3c49ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personalities" sheetId="16" r:id="R6aa8f950bb4548b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barks" sheetId="17" r:id="R0b8be5252ba04d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BarkSituations" sheetId="18" r:id="R413fe04458574faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestSettings" sheetId="19" r:id="R1a65972a7dd34625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestParts" sheetId="20" r:id="R55ffa531294f4ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestPersonalities" sheetId="21" r:id="R7927bc8331154817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestExclusions" sheetId="22" r:id="R6e058af231114ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrderRules" sheetId="23" r:id="Rb2478c11b6604fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endings" sheetId="24" r:id="R40b3788fa82148e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transitions" sheetId="25" r:id="R327b4a9d638d4f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIStrings" sheetId="26" r:id="R6d79db41f15545c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldGuide" sheetId="27" r:id="Re4c6b60f46794ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="28" r:id="R67c7e4576ee648c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -227,7 +227,7 @@
         <x:color rgb="FF9B560E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0D1"/>
         </x:patternFill>
       </x:fill>
@@ -237,7 +237,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -247,7 +247,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -257,7 +257,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -267,7 +267,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -277,7 +277,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -287,7 +287,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -297,7 +297,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -307,7 +307,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -317,7 +317,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -327,7 +327,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -337,7 +337,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -347,7 +347,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -357,7 +357,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -367,7 +367,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -377,7 +377,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -387,7 +387,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -397,7 +397,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -407,7 +407,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -417,7 +417,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -427,7 +427,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -437,7 +437,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -447,7 +447,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -457,7 +457,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -467,7 +467,7 @@
         <x:color rgb="FFB52222"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -4942,7 +4942,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19e927e7215f4870"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fc68c45be644f3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7622,7 +7622,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R400c62ee8cfe4b19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd7c3835b8a24d52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10474,7 +10474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a607d1bc77c4467"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4591661549e845e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10932,7 +10932,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2b841e30696457f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R642ac4cd0f3341c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11415,7 +11415,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85022a7099d6411e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34fe9e3b460f4fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11632,7 +11632,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7acf25d5f36244d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e93faf1019a48dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11945,7 +11945,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3643ab14ab054e7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdf1631cdde846d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13769,7 +13769,7 @@
     <x:row r="56" ht="26" customHeight="1">
       <x:c r="A56" s="18"/>
       <x:c r="B56" s="18" t="str">
-        <x:v>사람 무시하나 지금...</x:v>
+        <x:v>사람 &lt;fx=angry&gt;무시하나&lt;/fx&gt; 지금...</x:v>
       </x:c>
       <x:c r="C56" s="18" t="str">
         <x:v>Am I invisible or something...</x:v>
@@ -17792,7 +17792,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf20e812ed70440a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R088f006352094f8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18469,7 +18469,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc291b7b7ca5a4adf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R699aa7bce2c54319"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18758,7 +18758,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b1c10711cee47d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba20daa06c2249d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18959,7 +18959,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R633bbbc4f2f44cd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2a2f90bdf3408d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20287,7 +20287,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf51b88cb09934469"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9ef49ac203a4af1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20389,7 +20389,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85d38afd717c42b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4a12fd0d12d4248"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20646,7 +20646,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R838fa6e522a0490b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7087afe2b8594976"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20932,7 +20932,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605a10f7bae441d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf7b50b264844db4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21220,7 +21220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra200f98ec4dc4588"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49aa07f4005a4a3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21459,7 +21459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68ac777898624e1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb44d1338fe184562"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23188,7 +23188,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde139ccdf9ac47a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07ed4fc004404d5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24758,7 +24758,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cdc1c39de7e4b54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2eda82a7c61478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25266,7 +25266,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffb7a24eb77b486b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b3b57d15d7c4729"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28133,7 +28133,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8496b1df9e6d4772"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re37423dda8614123"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28364,7 +28364,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcad8e50371746c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45fd32b003fe425c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28667,7 +28667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0510f09f2d84138"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2a25ef00b094cde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29182,7 +29182,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d0850b6954a4ebf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra97e2d784d1646bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29505,7 +29505,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e4880cb4a45433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R938c208bdfdc4428"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32221,7 +32221,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2138096b1adf48ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c82c5f34e34d8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>